--- a/Result/profitability/6217.xlsx
+++ b/Result/profitability/6217.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.1</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.39</v>
+        <v>-0.4</v>
       </c>
       <c r="N2" t="n">
-        <v>21.6075</v>
+        <v>20.77875</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>-0.1</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.3750000000000001</v>
+        <v>-0.25875</v>
       </c>
       <c r="N3" t="n">
-        <v>21.24</v>
+        <v>21.725</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>0.22</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.19375</v>
+        <v>-0.1325</v>
       </c>
       <c r="N4" t="n">
-        <v>24.02875</v>
+        <v>24.17125</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>-0.41</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.14625</v>
+        <v>-0.095</v>
       </c>
       <c r="N5" t="n">
-        <v>24.57875</v>
+        <v>24.515</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-0.13</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.07375000000000001</v>
+        <v>-0.13125</v>
       </c>
       <c r="N6" t="n">
-        <v>25.74125</v>
+        <v>25.26375</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.29</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.05750000000000001</v>
+        <v>-0.0525</v>
       </c>
       <c r="N7" t="n">
-        <v>27.8475</v>
+        <v>28.2375</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>0.32</v>
       </c>
       <c r="M8" t="n">
-        <v>0.025</v>
+        <v>-0.02625</v>
       </c>
       <c r="N8" t="n">
-        <v>30.90125</v>
+        <v>30.4425</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>6217</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>1193</v>
+      </c>
+      <c r="D75" t="n">
+        <v>959</v>
+      </c>
+      <c r="E75" t="n">
+        <v>234</v>
+      </c>
+      <c r="F75" t="n">
+        <v>19.63</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-39</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-3.27%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-10</v>
+      </c>
+      <c r="J75" t="n">
+        <v>-49</v>
+      </c>
+      <c r="K75" t="n">
+        <v>-35</v>
+      </c>
+      <c r="L75" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="M75" t="n">
+        <v>-0.415</v>
+      </c>
+      <c r="N75" t="n">
+        <v>20.44125</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.41</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-3.727272727272727</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-3.670000000000002</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.157510729613734</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-0.5774647887323944</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-0.5100000000000016</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.02532274081429997</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
